--- a/iDeliver-Menu-Structure.xlsx
+++ b/iDeliver-Menu-Structure.xlsx
@@ -728,28 +728,28 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shops &amp; Partners</t>
+          <t xml:space="preserve">Cash &amp; Collections</t>
         </is>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partner Dues</t>
+          <t xml:space="preserve">Currency Check</t>
         </is>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">/partner-dues</t>
+          <t xml:space="preserve">/currency-check</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Handshake</t>
+          <t xml:space="preserve">ArrowRightLeft</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -783,20 +783,20 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplier Settlements</t>
+          <t xml:space="preserve">Partner Dues</t>
         </is>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">/supplier-settlements</t>
+          <t xml:space="preserve">/partner-dues</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store</t>
+          <t xml:space="preserve">Handshake</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -830,20 +830,20 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop Statements</t>
+          <t xml:space="preserve">Supplier Settlements</t>
         </is>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">/party-statements</t>
+          <t xml:space="preserve">/supplier-settlements</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wallet</t>
+          <t xml:space="preserve">Store</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -877,20 +877,20 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Products</t>
+          <t xml:space="preserve">Shop Statements</t>
         </is>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">/products</t>
+          <t xml:space="preserve">/party-statements</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tag</t>
+          <t xml:space="preserve">Wallet</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -924,20 +924,20 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inventory</t>
+          <t xml:space="preserve">Products</t>
         </is>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">/inventory</t>
+          <t xml:space="preserve">/products</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boxes</t>
+          <t xml:space="preserve">Tag</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -963,28 +963,28 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accounting</t>
+          <t xml:space="preserve">Shops &amp; Partners</t>
         </is>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Purchases</t>
+          <t xml:space="preserve">Inventory</t>
         </is>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">/purchase-invoices</t>
+          <t xml:space="preserve">/inventory</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">FileText</t>
+          <t xml:space="preserve">Boxes</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Price List</t>
+          <t xml:space="preserve">Purchases</t>
         </is>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">/price-list</t>
+          <t xml:space="preserve">/purchase-invoices</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ClipboardList</t>
+          <t xml:space="preserve">FileText</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1065,20 +1065,20 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Account Statements</t>
+          <t xml:space="preserve">Price List</t>
         </is>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">/account-statements</t>
+          <t xml:space="preserve">/price-list</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">BookText</t>
+          <t xml:space="preserve">ClipboardList</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1112,15 +1112,15 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Account Transactions</t>
+          <t xml:space="preserve">Account Statements</t>
         </is>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">/account-transactions</t>
+          <t xml:space="preserve">/account-statements</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1151,28 +1151,28 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">People &amp; Fleet</t>
+          <t xml:space="preserve">Accounting</t>
         </is>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suppliers</t>
+          <t xml:space="preserve">Account Transactions</t>
         </is>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">/contacts/suppliers</t>
+          <t xml:space="preserve">/account-transactions</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Building</t>
+          <t xml:space="preserve">BookText</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1206,20 +1206,20 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customers</t>
+          <t xml:space="preserve">Suppliers</t>
         </is>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">/contacts/customers</t>
+          <t xml:space="preserve">/contacts/suppliers</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">UserCheck</t>
+          <t xml:space="preserve">Building</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1253,20 +1253,20 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partners</t>
+          <t xml:space="preserve">Customers</t>
         </is>
       </c>
       <c r="F25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">/contacts/partners</t>
+          <t xml:space="preserve">/contacts/customers</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Handshake</t>
+          <t xml:space="preserve">UserCheck</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1300,20 +1300,20 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drivers</t>
+          <t xml:space="preserve">Partners</t>
         </is>
       </c>
       <c r="F26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">/drivers</t>
+          <t xml:space="preserve">/contacts/partners</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Users</t>
+          <t xml:space="preserve">Handshake</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1347,20 +1347,20 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vehicles</t>
+          <t xml:space="preserve">Drivers</t>
         </is>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">/vehicles</t>
+          <t xml:space="preserve">/drivers</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Car</t>
+          <t xml:space="preserve">Users</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1394,20 +1394,20 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Company</t>
+          <t xml:space="preserve">Vehicles</t>
         </is>
       </c>
       <c r="F28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">/company</t>
+          <t xml:space="preserve">/vehicles</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Building2</t>
+          <t xml:space="preserve">Car</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1433,28 +1433,28 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reports</t>
+          <t xml:space="preserve">People &amp; Fleet</t>
         </is>
       </c>
       <c r="D29">
+        <v>5</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Company</t>
+        </is>
+      </c>
+      <c r="F29">
         <v>6</v>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reports</t>
-        </is>
-      </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">/reports</t>
+          <t xml:space="preserve">/company</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">BarChart3</t>
+          <t xml:space="preserve">Building2</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1480,15 +1480,15 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Administration</t>
+          <t xml:space="preserve">Reports</t>
         </is>
       </c>
       <c r="D30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">App Settings</t>
+          <t xml:space="preserve">Reports</t>
         </is>
       </c>
       <c r="F30">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">/settings/app</t>
+          <t xml:space="preserve">/reports</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Settings</t>
+          <t xml:space="preserve">BarChart3</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin + Super admin</t>
+          <t xml:space="preserve">Everyone with office access</t>
         </is>
       </c>
       <c r="J30"/>
@@ -1535,20 +1535,20 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">User Accounts</t>
+          <t xml:space="preserve">App Settings</t>
         </is>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">/settings/users</t>
+          <t xml:space="preserve">/settings/app</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">UserCog</t>
+          <t xml:space="preserve">Settings</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1582,20 +1582,20 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subscriptions</t>
+          <t xml:space="preserve">User Accounts</t>
         </is>
       </c>
       <c r="F32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">/settings/subscriptions</t>
+          <t xml:space="preserve">/settings/users</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">CreditCard</t>
+          <t xml:space="preserve">UserCog</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1629,20 +1629,20 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software Subscriptions</t>
+          <t xml:space="preserve">Subscriptions</t>
         </is>
       </c>
       <c r="F33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">/settings/software-subscriptions</t>
+          <t xml:space="preserve">/settings/subscriptions</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">AppWindow</t>
+          <t xml:space="preserve">CreditCard</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1676,20 +1676,20 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Change Requests</t>
+          <t xml:space="preserve">Software Subscriptions</t>
         </is>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">/settings/change-requests</t>
+          <t xml:space="preserve">/settings/software-subscriptions</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">ClipboardPen</t>
+          <t xml:space="preserve">AppWindow</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1715,33 +1715,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Super Admin</t>
+          <t xml:space="preserve">Administration</t>
         </is>
       </c>
       <c r="D35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developer Account</t>
+          <t xml:space="preserve">Change Requests</t>
         </is>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">/settings/account</t>
+          <t xml:space="preserve">/settings/change-requests</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">ShieldCheck</t>
+          <t xml:space="preserve">ClipboardPen</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Super admin only</t>
+          <t xml:space="preserve">Admin + Super admin</t>
         </is>
       </c>
       <c r="J35"/>
@@ -1770,20 +1770,20 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Driver App (Collect)</t>
+          <t xml:space="preserve">Developer Account</t>
         </is>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">/settings/driver-collections</t>
+          <t xml:space="preserve">/settings/account</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Truck</t>
+          <t xml:space="preserve">ShieldCheck</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1817,20 +1817,20 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop Categories</t>
+          <t xml:space="preserve">Driver App (Collect)</t>
         </is>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">/settings/shop-categories</t>
+          <t xml:space="preserve">/settings/driver-collections</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tags</t>
+          <t xml:space="preserve">Truck</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1864,20 +1864,20 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Header Background</t>
+          <t xml:space="preserve">Shop Categories</t>
         </is>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">/settings/header-background</t>
+          <t xml:space="preserve">/settings/shop-categories</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ImageIcon</t>
+          <t xml:space="preserve">Tags</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1911,20 +1911,20 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Broadcast Messages</t>
+          <t xml:space="preserve">Header Background</t>
         </is>
       </c>
       <c r="F39">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">/settings/messages</t>
+          <t xml:space="preserve">/settings/header-background</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Megaphone</t>
+          <t xml:space="preserve">ImageIcon</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1958,20 +1958,20 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete Order</t>
+          <t xml:space="preserve">Broadcast Messages</t>
         </is>
       </c>
       <c r="F40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">/settings/delete-order</t>
+          <t xml:space="preserve">/settings/messages</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">PackageX</t>
+          <t xml:space="preserve">Megaphone</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2005,20 +2005,20 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete Orders by Date</t>
+          <t xml:space="preserve">Delete Order</t>
         </is>
       </c>
       <c r="F41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">/settings/delete-orders-range</t>
+          <t xml:space="preserve">/settings/delete-order</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">CalendarRange</t>
+          <t xml:space="preserve">PackageX</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2052,20 +2052,20 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reset Cashier Box</t>
+          <t xml:space="preserve">Delete Orders by Date</t>
         </is>
       </c>
       <c r="F42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">/settings/reset-cashier-box</t>
+          <t xml:space="preserve">/settings/delete-orders-range</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wallet</t>
+          <t xml:space="preserve">CalendarRange</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2099,20 +2099,20 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reset Data</t>
+          <t xml:space="preserve">Reset Cashier Box</t>
         </is>
       </c>
       <c r="F43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">/settings/reset</t>
+          <t xml:space="preserve">/settings/reset-cashier-box</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trash2</t>
+          <t xml:space="preserve">Wallet</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2127,8 +2127,55 @@
       <c r="N43"/>
       <c r="O43"/>
     </row>
+    <row r="44">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Menu fly-out</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Super Admin</t>
+        </is>
+      </c>
+      <c r="D44">
+        <v>8</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reset Data</t>
+        </is>
+      </c>
+      <c r="F44">
+        <v>9</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/settings/reset</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trash2</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Super admin only</t>
+        </is>
+      </c>
+      <c r="J44"/>
+      <c r="K44"/>
+      <c r="L44"/>
+      <c r="M44"/>
+      <c r="N44"/>
+      <c r="O44"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O43"/>
+  <autoFilter ref="A1:O44"/>
 </worksheet>
 </file>
 
